--- a/results/MC_Dist=Exp_n=300_LT=0.1_C=0.4_B=100.xlsx
+++ b/results/MC_Dist=Exp_n=300_LT=0.1_C=0.4_B=100.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -123,13 +123,16 @@
     <t xml:space="preserve">Gamma</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5,1</t>
+    <t xml:space="preserve">1,0.8</t>
   </si>
   <si>
     <t xml:space="preserve">x1.mean</t>
   </si>
   <si>
     <t xml:space="preserve">x1.sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8</t>
   </si>
   <si>
     <t xml:space="preserve">x2.mean</t>
@@ -545,22 +548,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.09297380957803</v>
+        <v>-1.09519395358928</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0929738095780295</v>
+        <v>-0.0951939535892823</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0640408483215807</v>
+        <v>0.056227829952536</v>
       </c>
       <c r="E2" t="n">
-        <v>0.23655080188589</v>
+        <v>0.218271310072083</v>
       </c>
       <c r="F2" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="G2" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="3">
@@ -568,22 +571,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.01827006994832</v>
+        <v>-1.03856014224063</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0182700699483218</v>
+        <v>-0.0385601422406314</v>
       </c>
       <c r="D3" t="n">
-        <v>0.019614788697511</v>
+        <v>0.0306442904300747</v>
       </c>
       <c r="E3" t="n">
-        <v>0.139555547181347</v>
+        <v>0.171615631897484</v>
       </c>
       <c r="F3" t="n">
         <v>0.95</v>
       </c>
       <c r="G3" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="4">
@@ -591,22 +594,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>1.54921327820245</v>
+        <v>1.09689252464425</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0492132782024475</v>
+        <v>0.0968925246442525</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0319061461828808</v>
+        <v>0.0511941485804868</v>
       </c>
       <c r="E4" t="n">
-        <v>0.172574678408295</v>
+        <v>0.205495182298832</v>
       </c>
       <c r="F4" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="G4" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="5">
@@ -614,22 +617,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>1.33182640351405</v>
+        <v>1.07138137484377</v>
       </c>
       <c r="C5" t="n">
-        <v>0.331826403514053</v>
+        <v>0.271381374843773</v>
       </c>
       <c r="D5" t="n">
-        <v>0.323404607755859</v>
+        <v>0.22359560788134</v>
       </c>
       <c r="E5" t="n">
-        <v>0.46416629474637</v>
+        <v>0.3891816813264</v>
       </c>
       <c r="F5" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="G5" t="n">
-        <v>0.97</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="6">
@@ -637,22 +640,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>1.99447184285637</v>
+        <v>1.98688501272409</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.00552815714363053</v>
+        <v>-0.0131149872759082</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0054673869832734</v>
+        <v>0.00716491234706877</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0741063013574251</v>
+        <v>0.084044898148967</v>
       </c>
       <c r="F6" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="G6" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
     </row>
   </sheetData>
@@ -783,20 +786,20 @@
         <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
@@ -815,2325 +818,2325 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-1.37415119604779</v>
+        <v>-1.1517100853078</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.05149017503711</v>
+        <v>-1.34509739568429</v>
       </c>
       <c r="C2" t="n">
-        <v>1.6978864253504</v>
+        <v>1.37227929007536</v>
       </c>
       <c r="D2" t="n">
-        <v>1.64315236396123</v>
+        <v>0.997801955486649</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.799014885737581</v>
+        <v>-0.834445018246267</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.62452907661786</v>
+        <v>-1.76680109680594</v>
       </c>
       <c r="G2" t="n">
-        <v>2.10570332753984</v>
+        <v>1.94643245089742</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-1.2623125918315</v>
+        <v>-0.78439602474356</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.942925666985363</v>
+        <v>-1.15716096667797</v>
       </c>
       <c r="C3" t="n">
-        <v>1.49034156810369</v>
+        <v>1.27817499374542</v>
       </c>
       <c r="D3" t="n">
-        <v>1.88681877997804</v>
+        <v>0.777322572330879</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.433176708068779</v>
+        <v>-1.39083413331193</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.08559143154044</v>
+        <v>-1.8265201121232</v>
       </c>
       <c r="G3" t="n">
-        <v>2.14696050065355</v>
+        <v>1.9198310863376</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-1.01491615376827</v>
+        <v>-1.07395379946633</v>
       </c>
       <c r="B4" t="n">
-        <v>-1.03840065763606</v>
+        <v>-0.900013775412796</v>
       </c>
       <c r="C4" t="n">
-        <v>1.40696853221392</v>
+        <v>0.748575203944518</v>
       </c>
       <c r="D4" t="n">
-        <v>1.26951179930254</v>
+        <v>0.972480342322547</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.13766747345824</v>
+        <v>-0.7723892579785</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.61269064655758</v>
+        <v>-1.30538646600557</v>
       </c>
       <c r="G4" t="n">
-        <v>1.96598749205161</v>
+        <v>1.93895758478152</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0.979947130885007</v>
+        <v>-0.914348995255695</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.08639025865676</v>
+        <v>-1.09384809054082</v>
       </c>
       <c r="C5" t="n">
-        <v>1.59453698391198</v>
+        <v>1.30684517396014</v>
       </c>
       <c r="D5" t="n">
-        <v>1.21078860922874</v>
+        <v>0.806930118247126</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.823968248534178</v>
+        <v>-1.12836391489195</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.49495361974651</v>
+        <v>-1.37132322730852</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9902849420965</v>
+        <v>2.08143991655607</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0.796236080206474</v>
+        <v>-1.64803506982187</v>
       </c>
       <c r="B6" t="n">
-        <v>-1.01379729452263</v>
+        <v>-1.14543942189387</v>
       </c>
       <c r="C6" t="n">
-        <v>1.53208842782895</v>
+        <v>1.3643423894599</v>
       </c>
       <c r="D6" t="n">
-        <v>1.04419001417184</v>
+        <v>2.06163379531495</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.38936656692852</v>
+        <v>-0.191672275035658</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.58416151382828</v>
+        <v>-0.764200395235648</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9646749284748</v>
+        <v>2.0005247275429</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-1.02644517099103</v>
+        <v>-1.35852173998835</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.07431427653102</v>
+        <v>-0.876117522552785</v>
       </c>
       <c r="C7" t="n">
-        <v>1.42237162092989</v>
+        <v>0.984314627709495</v>
       </c>
       <c r="D7" t="n">
-        <v>1.20583067058818</v>
+        <v>1.6198293470073</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.24543546991687</v>
+        <v>-0.728250054916942</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.32194994162703</v>
+        <v>-1.05269251586875</v>
       </c>
       <c r="G7" t="n">
-        <v>1.97926347998309</v>
+        <v>1.98683258781295</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0.872900305104527</v>
+        <v>-1.25993258188585</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.871395263262834</v>
+        <v>-1.00486945945296</v>
       </c>
       <c r="C8" t="n">
-        <v>1.28504690617677</v>
+        <v>1.07817140698358</v>
       </c>
       <c r="D8" t="n">
-        <v>0.887289163356427</v>
+        <v>1.28057182930593</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.05002549347783</v>
+        <v>-0.747140755048664</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.47466026128841</v>
+        <v>-1.26710539458779</v>
       </c>
       <c r="G8" t="n">
-        <v>1.99892038309551</v>
+        <v>1.96514542179707</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0.537336353161097</v>
+        <v>-1.05657215429997</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.0511368997861</v>
+        <v>-0.956018573646951</v>
       </c>
       <c r="C9" t="n">
-        <v>1.51848352017249</v>
+        <v>1.07700936770189</v>
       </c>
       <c r="D9" t="n">
-        <v>0.192074473787653</v>
+        <v>0.685771245123142</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.75791440729448</v>
+        <v>-0.558081886501897</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.57974635925198</v>
+        <v>-1.13658241831876</v>
       </c>
       <c r="G9" t="n">
-        <v>1.983002967469</v>
+        <v>2.00095785592086</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0.869279684768233</v>
+        <v>-0.898296755474085</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.10052729014649</v>
+        <v>-1.42812925588143</v>
       </c>
       <c r="C10" t="n">
-        <v>1.47076352382651</v>
+        <v>1.49091682122987</v>
       </c>
       <c r="D10" t="n">
-        <v>1.07361524289026</v>
+        <v>0.661766342512681</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.997946603770043</v>
+        <v>-1.15616545594254</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.69554239067706</v>
+        <v>-2.19728248831051</v>
       </c>
       <c r="G10" t="n">
-        <v>1.96852755593007</v>
+        <v>1.84341723817399</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-1.01190860229933</v>
+        <v>-1.32437528435415</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.780375000016725</v>
+        <v>-0.934992687410481</v>
       </c>
       <c r="C11" t="n">
-        <v>1.38290966913023</v>
+        <v>0.860812252478927</v>
       </c>
       <c r="D11" t="n">
-        <v>1.33085278614446</v>
+        <v>1.39541793443099</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.707561192719467</v>
+        <v>-0.7504739913738</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.43198988813072</v>
+        <v>-0.954667731316857</v>
       </c>
       <c r="G11" t="n">
-        <v>2.11897019228879</v>
+        <v>2.06949590268125</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-0.744133802868037</v>
+        <v>-1.10934280378744</v>
       </c>
       <c r="B12" t="n">
-        <v>-1.18163813958838</v>
+        <v>-1.68440607524192</v>
       </c>
       <c r="C12" t="n">
-        <v>1.57667815150651</v>
+        <v>1.66030395266912</v>
       </c>
       <c r="D12" t="n">
-        <v>0.685391902358514</v>
+        <v>0.980474733320716</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.41642107738021</v>
+        <v>-1.03025100027368</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.46271003961287</v>
+        <v>-2.07576559991457</v>
       </c>
       <c r="G12" t="n">
-        <v>1.94771329190753</v>
+        <v>1.84114622424012</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-1.45323218869858</v>
+        <v>-1.45436219826745</v>
       </c>
       <c r="B13" t="n">
-        <v>-1.25176168928617</v>
+        <v>-1.23792363695152</v>
       </c>
       <c r="C13" t="n">
-        <v>1.72127584509038</v>
+        <v>1.35450566562215</v>
       </c>
       <c r="D13" t="n">
-        <v>2.03681661802739</v>
+        <v>1.56920152278307</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.750935872440187</v>
+        <v>-0.781506869557267</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.86734109314366</v>
+        <v>-0.886878667935622</v>
       </c>
       <c r="G13" t="n">
-        <v>1.95685599959305</v>
+        <v>1.91021050086696</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-0.996928167407673</v>
+        <v>-1.03523265960415</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.903097722308725</v>
+        <v>-1.0299465168657</v>
       </c>
       <c r="C14" t="n">
-        <v>1.4895397043031</v>
+        <v>1.10109852499695</v>
       </c>
       <c r="D14" t="n">
-        <v>1.13784261820111</v>
+        <v>1.03656874263662</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.919005861624429</v>
+        <v>-1.15713914012448</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.54213540335787</v>
+        <v>-1.4825674043307</v>
       </c>
       <c r="G14" t="n">
-        <v>1.91419089430648</v>
+        <v>1.9678875509445</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-1.04968852452722</v>
+        <v>-0.877116972889997</v>
       </c>
       <c r="B15" t="n">
-        <v>-1.1381599128149</v>
+        <v>-0.803144719441549</v>
       </c>
       <c r="C15" t="n">
-        <v>1.66806357028209</v>
+        <v>0.864785777272784</v>
       </c>
       <c r="D15" t="n">
-        <v>1.19790543171104</v>
+        <v>0.701016642978295</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.827807929485367</v>
+        <v>-1.42290052354714</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.33191590314104</v>
+        <v>-2.4213952607317</v>
       </c>
       <c r="G15" t="n">
-        <v>2.00723034323683</v>
+        <v>2.12076418112272</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-1.26014242897094</v>
+        <v>-1.51246082632064</v>
       </c>
       <c r="B16" t="n">
-        <v>-1.34121036646409</v>
+        <v>-0.970024642551305</v>
       </c>
       <c r="C16" t="n">
-        <v>1.89374371619535</v>
+        <v>0.892373655849577</v>
       </c>
       <c r="D16" t="n">
-        <v>1.30794584023855</v>
+        <v>1.87220089750333</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.679280363346723</v>
+        <v>-0.8112353972959</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.967717122422451</v>
+        <v>-1.03004189757571</v>
       </c>
       <c r="G16" t="n">
-        <v>1.92954040785479</v>
+        <v>1.92183249348156</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-0.705041568260867</v>
+        <v>-1.03358129253563</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.938713785692569</v>
+        <v>-0.88667100357634</v>
       </c>
       <c r="C17" t="n">
-        <v>1.65947336340235</v>
+        <v>0.636168548819447</v>
       </c>
       <c r="D17" t="n">
-        <v>0.890264634342979</v>
+        <v>1.0007445698191</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.63920929759183</v>
+        <v>-0.945336608992866</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.83310058589795</v>
+        <v>-1.48057819568463</v>
       </c>
       <c r="G17" t="n">
-        <v>1.95704058677539</v>
+        <v>2.10905722845259</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-1.22905563455423</v>
+        <v>-0.90093204869494</v>
       </c>
       <c r="B18" t="n">
-        <v>-1.07513099202406</v>
+        <v>-0.783096610778092</v>
       </c>
       <c r="C18" t="n">
-        <v>1.65586261349478</v>
+        <v>0.950926752852623</v>
       </c>
       <c r="D18" t="n">
-        <v>1.79573624760837</v>
+        <v>0.840086944976334</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.619652691971792</v>
+        <v>-0.913382024483977</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.28532284561118</v>
+        <v>-1.48920019466031</v>
       </c>
       <c r="G18" t="n">
-        <v>2.00708436690121</v>
+        <v>2.04128059815639</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-0.717016458671121</v>
+        <v>-1.0283134392944</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.896876210079125</v>
+        <v>-1.29801993993587</v>
       </c>
       <c r="C19" t="n">
-        <v>1.64951984211199</v>
+        <v>1.21806241720463</v>
       </c>
       <c r="D19" t="n">
-        <v>0.442501909981395</v>
+        <v>0.716751616373683</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.966944322510453</v>
+        <v>-0.977003890390906</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.65901794554938</v>
+        <v>-1.85425220565088</v>
       </c>
       <c r="G19" t="n">
-        <v>2.10168077712429</v>
+        <v>1.87835491995995</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-1.16346685878351</v>
+        <v>-0.957568985966314</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.952876487797605</v>
+        <v>-0.997459647337382</v>
       </c>
       <c r="C20" t="n">
-        <v>1.41931995467671</v>
+        <v>1.25163275186612</v>
       </c>
       <c r="D20" t="n">
-        <v>1.29865622495839</v>
+        <v>0.823902482757156</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.721665825196368</v>
+        <v>-0.927176293013764</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.15531265086082</v>
+        <v>-1.4620249649343</v>
       </c>
       <c r="G20" t="n">
-        <v>2.08791731156015</v>
+        <v>2.05873383844896</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-1.16391259559374</v>
+        <v>-1.02726949332431</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.786830500886436</v>
+        <v>-0.965125931532184</v>
       </c>
       <c r="C21" t="n">
-        <v>1.15153336201422</v>
+        <v>0.866381614988706</v>
       </c>
       <c r="D21" t="n">
-        <v>1.52056363814647</v>
+        <v>0.856432158051928</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.734639038448421</v>
+        <v>-1.14843469716598</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.24091467536033</v>
+        <v>-1.44478984833106</v>
       </c>
       <c r="G21" t="n">
-        <v>2.02674618298988</v>
+        <v>1.91215873041138</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-1.30075711302277</v>
+        <v>-1.05990040235913</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.969368568540928</v>
+        <v>-0.972023427769929</v>
       </c>
       <c r="C22" t="n">
-        <v>1.4510442753539</v>
+        <v>1.02232088867902</v>
       </c>
       <c r="D22" t="n">
-        <v>1.82227914267466</v>
+        <v>0.976278178096618</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.750269740971379</v>
+        <v>-1.05586127418635</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.13472238052678</v>
+        <v>-1.99992695855312</v>
       </c>
       <c r="G22" t="n">
-        <v>2.04966123376911</v>
+        <v>1.99161157292047</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-0.984607197338627</v>
+        <v>-0.868437423899081</v>
       </c>
       <c r="B23" t="n">
-        <v>-1.08969858507694</v>
+        <v>-0.79783795952184</v>
       </c>
       <c r="C23" t="n">
-        <v>1.83861286712489</v>
+        <v>1.32192355065376</v>
       </c>
       <c r="D23" t="n">
-        <v>1.3023199917417</v>
+        <v>0.696174903580125</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.02683454740092</v>
+        <v>-0.936084825394198</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.60242737952707</v>
+        <v>-1.31611745593643</v>
       </c>
       <c r="G23" t="n">
-        <v>2.03078816893941</v>
+        <v>2.39204340552415</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-0.945474290106542</v>
+        <v>-1.0719617632596</v>
       </c>
       <c r="B24" t="n">
-        <v>-1.0136968626258</v>
+        <v>-0.901557367902424</v>
       </c>
       <c r="C24" t="n">
-        <v>1.70849553138667</v>
+        <v>0.743442305682043</v>
       </c>
       <c r="D24" t="n">
-        <v>1.00789083985476</v>
+        <v>1.07006024460802</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.768992535746147</v>
+        <v>-0.670531431042986</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.55753639523762</v>
+        <v>-1.35654655304752</v>
       </c>
       <c r="G24" t="n">
-        <v>2.12880504130594</v>
+        <v>1.91293075707683</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-1.0536723175744</v>
+        <v>-1.4495745665227</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.895467947941052</v>
+        <v>-1.03062635809364</v>
       </c>
       <c r="C25" t="n">
-        <v>1.54970213962599</v>
+        <v>0.824632990639224</v>
       </c>
       <c r="D25" t="n">
-        <v>1.30987899137174</v>
+        <v>1.4492541392784</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.81034703173155</v>
+        <v>-0.553055268838275</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.55490662186914</v>
+        <v>-0.785069949680825</v>
       </c>
       <c r="G25" t="n">
-        <v>2.00047818509124</v>
+        <v>1.95285719071218</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-0.996684398291234</v>
+        <v>-0.84921095815293</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.932925345459922</v>
+        <v>-1.17397147685221</v>
       </c>
       <c r="C26" t="n">
-        <v>1.49947857660658</v>
+        <v>1.41059850585838</v>
       </c>
       <c r="D26" t="n">
-        <v>0.891290456968982</v>
+        <v>0.439986184293788</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.03404568848875</v>
+        <v>-1.2504049784266</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.37616264825198</v>
+        <v>-2.23203030664904</v>
       </c>
       <c r="G26" t="n">
-        <v>2.00568656668848</v>
+        <v>2.03838002806694</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-1.02226578361786</v>
+        <v>-1.12983420986536</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.968759191970163</v>
+        <v>-0.944998862683329</v>
       </c>
       <c r="C27" t="n">
-        <v>1.47732778092164</v>
+        <v>0.929238845341749</v>
       </c>
       <c r="D27" t="n">
-        <v>1.21552890892241</v>
+        <v>0.994949086327976</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.22887669495994</v>
+        <v>-0.99347500663538</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.51533242265635</v>
+        <v>-2.05658667437219</v>
       </c>
       <c r="G27" t="n">
-        <v>2.01978092263279</v>
+        <v>1.97075734082634</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-1.21262075338152</v>
+        <v>-1.36589194322889</v>
       </c>
       <c r="B28" t="n">
-        <v>-1.15956911149192</v>
+        <v>-1.14776691685815</v>
       </c>
       <c r="C28" t="n">
-        <v>1.75405648429104</v>
+        <v>1.23017222381731</v>
       </c>
       <c r="D28" t="n">
-        <v>1.72395885000321</v>
+        <v>1.6509488289185</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.999864377182518</v>
+        <v>-0.857005532047015</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.29774652555875</v>
+        <v>-2.05531091869426</v>
       </c>
       <c r="G28" t="n">
-        <v>1.95291804638113</v>
+        <v>1.97610501874319</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>-1.27776849016734</v>
+        <v>-1.07246495734933</v>
       </c>
       <c r="B29" t="n">
-        <v>-1.01452561577915</v>
+        <v>-1.09774093948993</v>
       </c>
       <c r="C29" t="n">
-        <v>1.62435046458322</v>
+        <v>1.19841925341033</v>
       </c>
       <c r="D29" t="n">
-        <v>1.5045597221683</v>
+        <v>1.29756463490538</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.850046274891933</v>
+        <v>-1.26136933687662</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.16951361466864</v>
+        <v>-2.23059355592296</v>
       </c>
       <c r="G29" t="n">
-        <v>1.98677550945036</v>
+        <v>1.97603875526171</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>-0.836103427929106</v>
+        <v>-0.943460927432892</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.757506025721367</v>
+        <v>-1.34789708574691</v>
       </c>
       <c r="C30" t="n">
-        <v>1.37921202841093</v>
+        <v>1.36291782585606</v>
       </c>
       <c r="D30" t="n">
-        <v>0.751778762057211</v>
+        <v>0.823244822701834</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.3803023387917</v>
+        <v>-1.30924389968505</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.47034148770906</v>
+        <v>-1.50240549850823</v>
       </c>
       <c r="G30" t="n">
-        <v>1.98672493344755</v>
+        <v>1.97474484985411</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-1.10884067673339</v>
+        <v>-1.33672496378747</v>
       </c>
       <c r="B31" t="n">
-        <v>-1.03013876680985</v>
+        <v>-1.14034000196051</v>
       </c>
       <c r="C31" t="n">
-        <v>1.6182099892609</v>
+        <v>1.28691649619245</v>
       </c>
       <c r="D31" t="n">
-        <v>1.36408343886165</v>
+        <v>1.52962581268329</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.925892271220412</v>
+        <v>-0.821355714749734</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.45522124395109</v>
+        <v>-1.00392528937933</v>
       </c>
       <c r="G31" t="n">
-        <v>1.89411143039344</v>
+        <v>2.07697678875987</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-1.125874651824</v>
+        <v>-1.05329674280692</v>
       </c>
       <c r="B32" t="n">
-        <v>-1.05654796766008</v>
+        <v>-1.00187738301225</v>
       </c>
       <c r="C32" t="n">
-        <v>1.62469341669683</v>
+        <v>1.1539452959604</v>
       </c>
       <c r="D32" t="n">
-        <v>1.49547572466095</v>
+        <v>1.40134280274073</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.779528466785279</v>
+        <v>-1.16691953782973</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.52447549722196</v>
+        <v>-1.56882501355424</v>
       </c>
       <c r="G32" t="n">
-        <v>1.84442469082746</v>
+        <v>2.02067192289511</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-1.42095660892262</v>
+        <v>-1.66226894240492</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.754000138249612</v>
+        <v>-1.20921407582606</v>
       </c>
       <c r="C33" t="n">
-        <v>1.24327591422214</v>
+        <v>1.27204428355833</v>
       </c>
       <c r="D33" t="n">
-        <v>2.09973450556099</v>
+        <v>2.23349417730746</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.458297027827352</v>
+        <v>-0.303268969694189</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.06427363614251</v>
+        <v>-0.628897876759884</v>
       </c>
       <c r="G33" t="n">
-        <v>2.00380360187643</v>
+        <v>1.98830551437406</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>-1.07939270412502</v>
+        <v>-1.19941574904566</v>
       </c>
       <c r="B34" t="n">
-        <v>-1.18429429137223</v>
+        <v>-1.12835630209847</v>
       </c>
       <c r="C34" t="n">
-        <v>1.50170529712324</v>
+        <v>0.966117883977167</v>
       </c>
       <c r="D34" t="n">
-        <v>1.60593237227277</v>
+        <v>1.44590712202915</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.22686784974224</v>
+        <v>-1.07650011163002</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.55790338410339</v>
+        <v>-1.20727842669893</v>
       </c>
       <c r="G34" t="n">
-        <v>1.85267164530851</v>
+        <v>2.0772416354371</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-1.0401509017546</v>
+        <v>-0.900833745328909</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.921304318906425</v>
+        <v>-1.00973693589259</v>
       </c>
       <c r="C35" t="n">
-        <v>1.43748076686198</v>
+        <v>1.02442562114745</v>
       </c>
       <c r="D35" t="n">
-        <v>1.63776023852232</v>
+        <v>0.58514328900744</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.970169361705409</v>
+        <v>-0.874344299484647</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.76094110616357</v>
+        <v>-1.42271851001861</v>
       </c>
       <c r="G35" t="n">
-        <v>1.8767554368348</v>
+        <v>1.9809082429858</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>-1.13671862495838</v>
+        <v>-0.914174136331716</v>
       </c>
       <c r="B36" t="n">
-        <v>-1.12662762350828</v>
+        <v>-1.23050074086371</v>
       </c>
       <c r="C36" t="n">
-        <v>1.51428525275552</v>
+        <v>1.17081895587902</v>
       </c>
       <c r="D36" t="n">
-        <v>1.35113769501493</v>
+        <v>0.963224137947434</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.892287755749553</v>
+        <v>-1.25966851048753</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.39713152178557</v>
+        <v>-1.57341913646635</v>
       </c>
       <c r="G36" t="n">
-        <v>1.96633716197788</v>
+        <v>1.97629119412909</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-1.08354709995404</v>
+        <v>-1.38222472866611</v>
       </c>
       <c r="B37" t="n">
-        <v>-1.06908764910071</v>
+        <v>-1.13480128876584</v>
       </c>
       <c r="C37" t="n">
-        <v>1.27473682885743</v>
+        <v>1.23892981642917</v>
       </c>
       <c r="D37" t="n">
-        <v>1.74803119505615</v>
+        <v>1.51503740864008</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.820946106297877</v>
+        <v>-0.648239887321591</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.52437353115163</v>
+        <v>-1.87268940170589</v>
       </c>
       <c r="G37" t="n">
-        <v>1.95239996466568</v>
+        <v>1.95625914208461</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-1.09463694196581</v>
+        <v>-0.844002259268843</v>
       </c>
       <c r="B38" t="n">
-        <v>-1.02045299768127</v>
+        <v>-0.980135526819105</v>
       </c>
       <c r="C38" t="n">
-        <v>1.59415363436555</v>
+        <v>1.10727673022194</v>
       </c>
       <c r="D38" t="n">
-        <v>1.6486958887544</v>
+        <v>0.634930211750147</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.23566362276779</v>
+        <v>-1.1062933654669</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.36104155284976</v>
+        <v>-1.58221659103629</v>
       </c>
       <c r="G38" t="n">
-        <v>2.09338618635015</v>
+        <v>2.05977998722674</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>-1.27602993831776</v>
+        <v>-1.27545059210409</v>
       </c>
       <c r="B39" t="n">
-        <v>-1.07808301078246</v>
+        <v>-0.915728697207705</v>
       </c>
       <c r="C39" t="n">
-        <v>1.6514193742876</v>
+        <v>0.969576950639268</v>
       </c>
       <c r="D39" t="n">
-        <v>1.7010290384233</v>
+        <v>1.44377166368747</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.915447342083791</v>
+        <v>-0.505397318915959</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.8658947907312</v>
+        <v>-1.15375360459671</v>
       </c>
       <c r="G39" t="n">
-        <v>2.04904036505638</v>
+        <v>1.99211569604734</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>-1.2754469333442</v>
+        <v>-1.0998354889513</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.774169215165261</v>
+        <v>-1.01380099693452</v>
       </c>
       <c r="C40" t="n">
-        <v>1.40267669372558</v>
+        <v>1.20020189285977</v>
       </c>
       <c r="D40" t="n">
-        <v>1.91013503715205</v>
+        <v>1.04026255062614</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.908390356926331</v>
+        <v>-0.915408628044675</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.25846391310505</v>
+        <v>-1.26780899980838</v>
       </c>
       <c r="G40" t="n">
-        <v>2.1979422274462</v>
+        <v>1.98126766727645</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-0.964444275613423</v>
+        <v>-0.809683863174043</v>
       </c>
       <c r="B41" t="n">
-        <v>-0.813012885290989</v>
+        <v>-0.880050030299935</v>
       </c>
       <c r="C41" t="n">
-        <v>1.02314261067237</v>
+        <v>0.872203965345285</v>
       </c>
       <c r="D41" t="n">
-        <v>1.01387183637294</v>
+        <v>0.642161934475203</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.917713883617917</v>
+        <v>-1.2498122416285</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.56741934033125</v>
+        <v>-1.67024295872016</v>
       </c>
       <c r="G41" t="n">
-        <v>1.9909396482809</v>
+        <v>1.94536134263085</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>-1.65750014921654</v>
+        <v>-1.16578516819161</v>
       </c>
       <c r="B42" t="n">
-        <v>-1.14822140462744</v>
+        <v>-1.04667482925984</v>
       </c>
       <c r="C42" t="n">
-        <v>1.53837935773682</v>
+        <v>1.19058477537709</v>
       </c>
       <c r="D42" t="n">
-        <v>2.34747976469191</v>
+        <v>1.17179721656797</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.45661734328878</v>
+        <v>-0.910725624232662</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.973254975382869</v>
+        <v>-1.28938694989671</v>
       </c>
       <c r="G42" t="n">
-        <v>1.93209051872276</v>
+        <v>1.93962059091959</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>-1.36042873556403</v>
+        <v>-0.972905820610934</v>
       </c>
       <c r="B43" t="n">
-        <v>-1.39251530266994</v>
+        <v>-1.12461477539508</v>
       </c>
       <c r="C43" t="n">
-        <v>2.00320186085278</v>
+        <v>1.12319172687023</v>
       </c>
       <c r="D43" t="n">
-        <v>1.52286788408724</v>
+        <v>1.1887755506303</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.835646449339853</v>
+        <v>-1.13876734332435</v>
       </c>
       <c r="F43" t="n">
-        <v>-1.69057189805369</v>
+        <v>-1.57749845080287</v>
       </c>
       <c r="G43" t="n">
-        <v>1.86614514183184</v>
+        <v>2.01863522309022</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>-0.949686717220932</v>
+        <v>-1.57458904761776</v>
       </c>
       <c r="B44" t="n">
-        <v>-0.920442135998001</v>
+        <v>-0.807214347251559</v>
       </c>
       <c r="C44" t="n">
-        <v>1.36363885046952</v>
+        <v>0.777785991976941</v>
       </c>
       <c r="D44" t="n">
-        <v>1.00561354505985</v>
+        <v>1.87559976369471</v>
       </c>
       <c r="E44" t="n">
-        <v>-1.41528343642828</v>
+        <v>-0.422321965945586</v>
       </c>
       <c r="F44" t="n">
-        <v>-1.65419173145146</v>
+        <v>-0.73110605464761</v>
       </c>
       <c r="G44" t="n">
-        <v>1.88233294372592</v>
+        <v>2.0801484932863</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>-1.28636975601722</v>
+        <v>-1.42536955404692</v>
       </c>
       <c r="B45" t="n">
-        <v>-1.27077703172562</v>
+        <v>-1.22907314844918</v>
       </c>
       <c r="C45" t="n">
-        <v>1.60295632007797</v>
+        <v>1.34881584490135</v>
       </c>
       <c r="D45" t="n">
-        <v>1.88877967818365</v>
+        <v>1.34216122714565</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.823538990910777</v>
+        <v>-0.609160835380861</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.43161241348496</v>
+        <v>-1.67215696390412</v>
       </c>
       <c r="G45" t="n">
-        <v>1.93953398463142</v>
+        <v>1.9105739715256</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>-1.24049388714104</v>
+        <v>-1.01899992602417</v>
       </c>
       <c r="B46" t="n">
-        <v>-1.01140027868337</v>
+        <v>-0.953168767002054</v>
       </c>
       <c r="C46" t="n">
-        <v>1.58452513530702</v>
+        <v>0.904762225848066</v>
       </c>
       <c r="D46" t="n">
-        <v>1.52388790059335</v>
+        <v>1.14937989632416</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.961906918647975</v>
+        <v>-0.990652245979116</v>
       </c>
       <c r="F46" t="n">
-        <v>-2.07495889283998</v>
+        <v>-1.5193510838023</v>
       </c>
       <c r="G46" t="n">
-        <v>1.9752588566988</v>
+        <v>1.90689376402967</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>-1.34008137042353</v>
+        <v>-0.973455620647561</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.908010209664722</v>
+        <v>-0.757042257060712</v>
       </c>
       <c r="C47" t="n">
-        <v>1.6534924211157</v>
+        <v>0.881085576414359</v>
       </c>
       <c r="D47" t="n">
-        <v>1.90456700766108</v>
+        <v>0.952231256621076</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.534399197886786</v>
+        <v>-0.949323074501507</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.12683158077242</v>
+        <v>-1.42181749807203</v>
       </c>
       <c r="G47" t="n">
-        <v>2.09823673576607</v>
+        <v>2.1632728344119</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>-1.11253198857326</v>
+        <v>-1.0886316698563</v>
       </c>
       <c r="B48" t="n">
-        <v>-1.08014143389513</v>
+        <v>-0.771267704726989</v>
       </c>
       <c r="C48" t="n">
-        <v>1.58067072708591</v>
+        <v>0.86141316654573</v>
       </c>
       <c r="D48" t="n">
-        <v>1.55753862533667</v>
+        <v>1.23714291781808</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.802866075834099</v>
+        <v>-0.800704418443425</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.38175177384127</v>
+        <v>-1.40658690761757</v>
       </c>
       <c r="G48" t="n">
-        <v>2.11000628627915</v>
+        <v>1.92904687164974</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>-1.25067138770272</v>
+        <v>-1.32377324349736</v>
       </c>
       <c r="B49" t="n">
-        <v>-0.923333211143591</v>
+        <v>-1.61216067163185</v>
       </c>
       <c r="C49" t="n">
-        <v>1.55246361797929</v>
+        <v>1.63821987291294</v>
       </c>
       <c r="D49" t="n">
-        <v>1.66247327636111</v>
+        <v>1.41623952820092</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.942755577219661</v>
+        <v>-0.823249252649335</v>
       </c>
       <c r="F49" t="n">
-        <v>-2.23843772042999</v>
+        <v>-1.82126845395003</v>
       </c>
       <c r="G49" t="n">
-        <v>1.95291448885354</v>
+        <v>1.93433274051514</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-1.47185574083355</v>
+        <v>-0.803285993450898</v>
       </c>
       <c r="B50" t="n">
-        <v>-1.03431173739556</v>
+        <v>-1.2074551791836</v>
       </c>
       <c r="C50" t="n">
-        <v>1.56437830988324</v>
+        <v>1.24341702755058</v>
       </c>
       <c r="D50" t="n">
-        <v>2.14567406860574</v>
+        <v>0.718098160344854</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.820636015111291</v>
+        <v>-1.44739302396411</v>
       </c>
       <c r="F50" t="n">
-        <v>-2.07990766759843</v>
+        <v>-1.71086969048554</v>
       </c>
       <c r="G50" t="n">
-        <v>2.00138518783079</v>
+        <v>2.04057967012232</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>-1.48294618772252</v>
+        <v>-1.16777647080567</v>
       </c>
       <c r="B51" t="n">
-        <v>-1.02927732434005</v>
+        <v>-1.21751839986081</v>
       </c>
       <c r="C51" t="n">
-        <v>1.56806408030208</v>
+        <v>1.1870826931877</v>
       </c>
       <c r="D51" t="n">
-        <v>2.12070704526072</v>
+        <v>1.21815313322457</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.627146568028151</v>
+        <v>-0.549822556143592</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.07610634511196</v>
+        <v>-1.37585466820998</v>
       </c>
       <c r="G51" t="n">
-        <v>1.99858741466825</v>
+        <v>1.91433862210992</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>-1.11287716477374</v>
+        <v>-1.22798469391792</v>
       </c>
       <c r="B52" t="n">
-        <v>-1.21948837386593</v>
+        <v>-1.27907695943656</v>
       </c>
       <c r="C52" t="n">
-        <v>1.70607414996823</v>
+        <v>1.35511458763698</v>
       </c>
       <c r="D52" t="n">
-        <v>1.123918410646</v>
+        <v>1.45877930419534</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.948732615417684</v>
+        <v>-0.890877186684028</v>
       </c>
       <c r="F52" t="n">
-        <v>-2.11210952917336</v>
+        <v>-1.50373534633057</v>
       </c>
       <c r="G52" t="n">
-        <v>1.90289742942615</v>
+        <v>1.94398231033507</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>-1.18264211198636</v>
+        <v>-1.61846851861563</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.778293768130611</v>
+        <v>-1.02782848199432</v>
       </c>
       <c r="C53" t="n">
-        <v>1.42316850517502</v>
+        <v>1.04097189282794</v>
       </c>
       <c r="D53" t="n">
-        <v>1.30036714074277</v>
+        <v>1.85009124280414</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.610555430576931</v>
+        <v>-0.32612267442446</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.19508793950599</v>
+        <v>-0.575872458244259</v>
       </c>
       <c r="G53" t="n">
-        <v>1.99203705539956</v>
+        <v>2.01558150217917</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>-0.866873180889206</v>
+        <v>-0.879950033528913</v>
       </c>
       <c r="B54" t="n">
-        <v>-0.964301979657911</v>
+        <v>-0.730791052978091</v>
       </c>
       <c r="C54" t="n">
-        <v>1.63178438891656</v>
+        <v>0.788305602074256</v>
       </c>
       <c r="D54" t="n">
-        <v>0.766678908420437</v>
+        <v>0.379551266451711</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.44496479794158</v>
+        <v>-0.872801393549922</v>
       </c>
       <c r="F54" t="n">
-        <v>-2.49715336114451</v>
+        <v>-1.39549869703843</v>
       </c>
       <c r="G54" t="n">
-        <v>2.08302363869521</v>
+        <v>2.00612509899858</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>-1.05360865640737</v>
+        <v>-1.36704681522507</v>
       </c>
       <c r="B55" t="n">
-        <v>-1.02510906537107</v>
+        <v>-1.23704059340574</v>
       </c>
       <c r="C55" t="n">
-        <v>1.53618771513509</v>
+        <v>1.51126862427743</v>
       </c>
       <c r="D55" t="n">
-        <v>1.15917066092704</v>
+        <v>1.82494429726094</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.24663636990781</v>
+        <v>-0.951735396120285</v>
       </c>
       <c r="F55" t="n">
-        <v>-2.06052789001935</v>
+        <v>-1.91262412267631</v>
       </c>
       <c r="G55" t="n">
-        <v>2.0656317020123</v>
+        <v>1.96585934466691</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>-0.96632805631834</v>
+        <v>-0.940009910385536</v>
       </c>
       <c r="B56" t="n">
-        <v>-1.01058518234495</v>
+        <v>-0.958233318906091</v>
       </c>
       <c r="C56" t="n">
-        <v>1.47277785173563</v>
+        <v>0.857365424971156</v>
       </c>
       <c r="D56" t="n">
-        <v>0.955484070269031</v>
+        <v>0.878190430586984</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.16216810240282</v>
+        <v>-1.0335316767891</v>
       </c>
       <c r="F56" t="n">
-        <v>-2.27456670408424</v>
+        <v>-1.5391462015377</v>
       </c>
       <c r="G56" t="n">
-        <v>1.96260657272552</v>
+        <v>1.99015238030302</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>-1.60592153903315</v>
+        <v>-0.939516437777316</v>
       </c>
       <c r="B57" t="n">
-        <v>-1.33789602011527</v>
+        <v>-1.15319313658784</v>
       </c>
       <c r="C57" t="n">
-        <v>1.75708249987499</v>
+        <v>1.18807307794249</v>
       </c>
       <c r="D57" t="n">
-        <v>2.32776511328645</v>
+        <v>0.428763959437886</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.829198015097092</v>
+        <v>-1.06223011623087</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.74697516735883</v>
+        <v>-1.91614063276972</v>
       </c>
       <c r="G57" t="n">
-        <v>1.92157156340125</v>
+        <v>1.8264393393881</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>-1.09410730381623</v>
+        <v>-1.01135307344888</v>
       </c>
       <c r="B58" t="n">
-        <v>-0.854496322414308</v>
+        <v>-1.01414213043452</v>
       </c>
       <c r="C58" t="n">
-        <v>1.58413927338573</v>
+        <v>1.00554425697898</v>
       </c>
       <c r="D58" t="n">
-        <v>1.4091374916976</v>
+        <v>0.73983456775623</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.12939032374987</v>
+        <v>-1.10400646874062</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.52997992689136</v>
+        <v>-2.32927802016823</v>
       </c>
       <c r="G58" t="n">
-        <v>2.027592654283</v>
+        <v>1.93301837735384</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>-1.2012690247016</v>
+        <v>-0.816535928058416</v>
       </c>
       <c r="B59" t="n">
-        <v>-1.00583471938371</v>
+        <v>-1.14141566932375</v>
       </c>
       <c r="C59" t="n">
-        <v>1.42818689146029</v>
+        <v>1.16657278279461</v>
       </c>
       <c r="D59" t="n">
-        <v>1.73645617148107</v>
+        <v>0.453326871073693</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.711722051602952</v>
+        <v>-1.32921552547426</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.17254743601676</v>
+        <v>-2.3202672424335</v>
       </c>
       <c r="G59" t="n">
-        <v>1.93539512154641</v>
+        <v>1.92298225878574</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>-0.762413274486883</v>
+        <v>-0.908756634781235</v>
       </c>
       <c r="B60" t="n">
-        <v>-0.774367499230967</v>
+        <v>-1.13537290903063</v>
       </c>
       <c r="C60" t="n">
-        <v>1.55957336480956</v>
+        <v>1.34623204045008</v>
       </c>
       <c r="D60" t="n">
-        <v>0.458892288625936</v>
+        <v>0.484125661867997</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.17844143376623</v>
+        <v>-0.804894373073796</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.56945556778632</v>
+        <v>-1.23822558132508</v>
       </c>
       <c r="G60" t="n">
-        <v>2.04534634418142</v>
+        <v>2.05115391701544</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>-0.857228761838673</v>
+        <v>-1.32018639378006</v>
       </c>
       <c r="B61" t="n">
-        <v>-1.12344419981276</v>
+        <v>-1.18044437268726</v>
       </c>
       <c r="C61" t="n">
-        <v>1.61098852523017</v>
+        <v>1.05084288218271</v>
       </c>
       <c r="D61" t="n">
-        <v>0.789445889673422</v>
+        <v>1.77101542564107</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.39186686963043</v>
+        <v>-0.965781336143791</v>
       </c>
       <c r="F61" t="n">
-        <v>-2.44215568504078</v>
+        <v>-1.94975923221042</v>
       </c>
       <c r="G61" t="n">
-        <v>2.0517734988838</v>
+        <v>1.98820546187056</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>-1.00437631472696</v>
+        <v>-1.10192111406463</v>
       </c>
       <c r="B62" t="n">
-        <v>-0.852609820164982</v>
+        <v>-0.968543316672377</v>
       </c>
       <c r="C62" t="n">
-        <v>1.56420994562995</v>
+        <v>1.22294094502223</v>
       </c>
       <c r="D62" t="n">
-        <v>1.12007115343508</v>
+        <v>1.22721541698951</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.676762003705546</v>
+        <v>-0.895476444120165</v>
       </c>
       <c r="F62" t="n">
-        <v>-1.29499491284177</v>
+        <v>-1.27164430543291</v>
       </c>
       <c r="G62" t="n">
-        <v>2.02315472961767</v>
+        <v>2.067570669237</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>-0.857963452052511</v>
+        <v>-1.07775008473328</v>
       </c>
       <c r="B63" t="n">
-        <v>-0.925258521603942</v>
+        <v>-1.01972938548086</v>
       </c>
       <c r="C63" t="n">
-        <v>1.64190837355726</v>
+        <v>1.1237680253765</v>
       </c>
       <c r="D63" t="n">
-        <v>1.14931928984289</v>
+        <v>0.937373000694428</v>
       </c>
       <c r="E63" t="n">
-        <v>-1.32470484421815</v>
+        <v>-0.867715390954422</v>
       </c>
       <c r="F63" t="n">
-        <v>-1.70612136575122</v>
+        <v>-2.00474152926857</v>
       </c>
       <c r="G63" t="n">
-        <v>2.05132382930213</v>
+        <v>2.05176418378356</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>-1.38570249146402</v>
+        <v>-1.07406715619301</v>
       </c>
       <c r="B64" t="n">
-        <v>-1.28742819628012</v>
+        <v>-0.893431260486158</v>
       </c>
       <c r="C64" t="n">
-        <v>1.86408127181879</v>
+        <v>1.0012193371974</v>
       </c>
       <c r="D64" t="n">
-        <v>1.59442855119543</v>
+        <v>0.900653322162261</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.223179555950957</v>
+        <v>-0.636541124988054</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.711383036820273</v>
+        <v>-1.25034846488864</v>
       </c>
       <c r="G64" t="n">
-        <v>2.01837346414726</v>
+        <v>1.9622700596811</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>-1.06187335447297</v>
+        <v>-1.0590874706836</v>
       </c>
       <c r="B65" t="n">
-        <v>-1.03492149220027</v>
+        <v>-0.88621899156834</v>
       </c>
       <c r="C65" t="n">
-        <v>1.52309982475191</v>
+        <v>0.845366244019758</v>
       </c>
       <c r="D65" t="n">
-        <v>1.18799864196424</v>
+        <v>0.929166690983074</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.835620157911216</v>
+        <v>-0.541943069225378</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.42555708005665</v>
+        <v>-1.15204086608246</v>
       </c>
       <c r="G65" t="n">
-        <v>2.00343664722765</v>
+        <v>2.03303576425562</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>-0.872543960693062</v>
+        <v>-1.06470605674203</v>
       </c>
       <c r="B66" t="n">
-        <v>-1.04072286792621</v>
+        <v>-1.00582265474378</v>
       </c>
       <c r="C66" t="n">
-        <v>1.63362380131772</v>
+        <v>0.976183334728978</v>
       </c>
       <c r="D66" t="n">
-        <v>0.548954140332224</v>
+        <v>1.05522290527721</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.13554033085949</v>
+        <v>-1.14248764391247</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.48123368763718</v>
+        <v>-1.38319902875573</v>
       </c>
       <c r="G66" t="n">
-        <v>1.97343783860561</v>
+        <v>1.95965352917564</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>-1.12901052556566</v>
+        <v>-1.06673484329246</v>
       </c>
       <c r="B67" t="n">
-        <v>-1.27313103854042</v>
+        <v>-1.22983151195532</v>
       </c>
       <c r="C67" t="n">
-        <v>1.90542684493792</v>
+        <v>1.34942592228513</v>
       </c>
       <c r="D67" t="n">
-        <v>1.85981579995484</v>
+        <v>1.0272802235368</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.3423341953134</v>
+        <v>-1.12477071689932</v>
       </c>
       <c r="F67" t="n">
-        <v>-2.53151807713374</v>
+        <v>-2.28643335228771</v>
       </c>
       <c r="G67" t="n">
-        <v>1.96015289352172</v>
+        <v>1.95559396399862</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>-0.917335555632963</v>
+        <v>-0.863583864315134</v>
       </c>
       <c r="B68" t="n">
-        <v>-1.10711251458697</v>
+        <v>-0.882280338854126</v>
       </c>
       <c r="C68" t="n">
-        <v>1.49272377386467</v>
+        <v>0.844306964918413</v>
       </c>
       <c r="D68" t="n">
-        <v>1.3216086118758</v>
+        <v>0.707411504755843</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.39901496251117</v>
+        <v>-0.979457481242</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.74351057753999</v>
+        <v>-1.54421230859352</v>
       </c>
       <c r="G68" t="n">
-        <v>1.85420070663735</v>
+        <v>1.89094021491425</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>-1.06022463789062</v>
+        <v>-1.00799338134444</v>
       </c>
       <c r="B69" t="n">
-        <v>-0.9652995574639</v>
+        <v>-1.1306936511335</v>
       </c>
       <c r="C69" t="n">
-        <v>1.43628809947819</v>
+        <v>1.12483771021625</v>
       </c>
       <c r="D69" t="n">
-        <v>0.960363078645291</v>
+        <v>0.588955919605065</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.0084995408706</v>
+        <v>-0.738594710828889</v>
       </c>
       <c r="F69" t="n">
-        <v>-2.05211582235701</v>
+        <v>-2.00607207153954</v>
       </c>
       <c r="G69" t="n">
-        <v>2.11259649942158</v>
+        <v>1.93470608953836</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>-1.17225025768228</v>
+        <v>-1.18899439661347</v>
       </c>
       <c r="B70" t="n">
-        <v>-0.871866777332118</v>
+        <v>-0.908813069821724</v>
       </c>
       <c r="C70" t="n">
-        <v>1.4587283925897</v>
+        <v>1.04250108120787</v>
       </c>
       <c r="D70" t="n">
-        <v>1.47461225676575</v>
+        <v>1.28540645867578</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.885461404937789</v>
+        <v>-0.875231187643925</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.09919837254448</v>
+        <v>-1.15634873590192</v>
       </c>
       <c r="G70" t="n">
-        <v>2.0607210087289</v>
+        <v>2.01309735541358</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>-0.849040857921852</v>
+        <v>-1.1698743890317</v>
       </c>
       <c r="B71" t="n">
-        <v>-0.982070259564542</v>
+        <v>-1.23905472016458</v>
       </c>
       <c r="C71" t="n">
-        <v>1.41375640609037</v>
+        <v>1.06079295239675</v>
       </c>
       <c r="D71" t="n">
-        <v>0.781509580588431</v>
+        <v>1.19925171057033</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.17074775078676</v>
+        <v>-0.88537612532669</v>
       </c>
       <c r="F71" t="n">
-        <v>-2.55210188425023</v>
+        <v>-2.06626511158585</v>
       </c>
       <c r="G71" t="n">
-        <v>1.9875826637414</v>
+        <v>1.9115527874636</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>-1.22884025088715</v>
+        <v>-0.940455112007925</v>
       </c>
       <c r="B72" t="n">
-        <v>-1.09538081150621</v>
+        <v>-1.00432299170545</v>
       </c>
       <c r="C72" t="n">
-        <v>1.7350568887075</v>
+        <v>1.08193933607638</v>
       </c>
       <c r="D72" t="n">
-        <v>1.53341899347023</v>
+        <v>1.02366292919553</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.01463400191875</v>
+        <v>-1.07615484282557</v>
       </c>
       <c r="F72" t="n">
-        <v>-2.10966920622903</v>
+        <v>-1.72766239842544</v>
       </c>
       <c r="G72" t="n">
-        <v>1.92347872862494</v>
+        <v>1.94448640246989</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>-0.872209134266471</v>
+        <v>-0.634728782117862</v>
       </c>
       <c r="B73" t="n">
-        <v>-0.926277899532926</v>
+        <v>-1.01563123858084</v>
       </c>
       <c r="C73" t="n">
-        <v>1.7533238627946</v>
+        <v>1.07107077797475</v>
       </c>
       <c r="D73" t="n">
-        <v>0.8027942621452</v>
+        <v>0.750623714579064</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.33887882955985</v>
+        <v>-1.66303466643289</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.75263585623952</v>
+        <v>-2.07072641205982</v>
       </c>
       <c r="G73" t="n">
-        <v>2.09980504655253</v>
+        <v>1.83726205432947</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-0.803561251250226</v>
+        <v>-1.05993287110741</v>
       </c>
       <c r="B74" t="n">
-        <v>-0.978326336920274</v>
+        <v>-0.936996270680289</v>
       </c>
       <c r="C74" t="n">
-        <v>1.43580866900459</v>
+        <v>1.34199055280075</v>
       </c>
       <c r="D74" t="n">
-        <v>0.853844913300331</v>
+        <v>1.09532287881985</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.13128934316809</v>
+        <v>-1.28832462506644</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.57800673403846</v>
+        <v>-1.330792037537</v>
       </c>
       <c r="G74" t="n">
-        <v>1.8599925955006</v>
+        <v>2.03378140587367</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>-1.52913426774372</v>
+        <v>-0.951749785099053</v>
       </c>
       <c r="B75" t="n">
-        <v>-1.10305417575133</v>
+        <v>-1.02189756501841</v>
       </c>
       <c r="C75" t="n">
-        <v>1.7556271262989</v>
+        <v>1.10523557106946</v>
       </c>
       <c r="D75" t="n">
-        <v>2.09400038311463</v>
+        <v>1.03442805947318</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.329397407505744</v>
+        <v>-1.03847167764193</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.962162971722499</v>
+        <v>-1.45266904565527</v>
       </c>
       <c r="G75" t="n">
-        <v>1.98597561519513</v>
+        <v>2.02436535628497</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>-0.846686824816935</v>
+        <v>-0.865606717196048</v>
       </c>
       <c r="B76" t="n">
-        <v>-0.881227497322259</v>
+        <v>-0.875168530298371</v>
       </c>
       <c r="C76" t="n">
-        <v>1.43724425287696</v>
+        <v>1.03536410890573</v>
       </c>
       <c r="D76" t="n">
-        <v>0.966345632213871</v>
+        <v>0.603730714802404</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.17951032471056</v>
+        <v>-1.16886056279376</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.58836826544934</v>
+        <v>-1.57147045473322</v>
       </c>
       <c r="G76" t="n">
-        <v>2.03273583495665</v>
+        <v>2.07363070289538</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>-1.02745824703977</v>
+        <v>-1.07825035740527</v>
       </c>
       <c r="B77" t="n">
-        <v>-1.01989432147357</v>
+        <v>-1.04745458285187</v>
       </c>
       <c r="C77" t="n">
-        <v>1.45198663661224</v>
+        <v>1.13401901486668</v>
       </c>
       <c r="D77" t="n">
-        <v>1.23262941047248</v>
+        <v>1.2482550534195</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.06040613199781</v>
+        <v>-0.586327082873754</v>
       </c>
       <c r="F77" t="n">
-        <v>-2.14136402674847</v>
+        <v>-1.3760784107616</v>
       </c>
       <c r="G77" t="n">
-        <v>1.94076918387496</v>
+        <v>2.03726514091091</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>-1.12627439199238</v>
+        <v>-0.865423895567417</v>
       </c>
       <c r="B78" t="n">
-        <v>-1.09354151820795</v>
+        <v>-0.948299448704019</v>
       </c>
       <c r="C78" t="n">
-        <v>1.74834441916467</v>
+        <v>0.926219911456415</v>
       </c>
       <c r="D78" t="n">
-        <v>1.29438731322841</v>
+        <v>0.637563137565202</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.04755855927974</v>
+        <v>-1.14033998407971</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.08257889440657</v>
+        <v>-1.52136049811955</v>
       </c>
       <c r="G78" t="n">
-        <v>2.06515513885479</v>
+        <v>2.03948032923171</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>-1.03781484234169</v>
+        <v>-0.989843958261535</v>
       </c>
       <c r="B79" t="n">
-        <v>-0.913692890886292</v>
+        <v>-1.04097690927625</v>
       </c>
       <c r="C79" t="n">
-        <v>1.39090886086803</v>
+        <v>0.969991810867369</v>
       </c>
       <c r="D79" t="n">
-        <v>1.1597818560852</v>
+        <v>1.04828293991687</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.17074150511295</v>
+        <v>-0.9370106848528</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.2755344962294</v>
+        <v>-1.48440580536387</v>
       </c>
       <c r="G79" t="n">
-        <v>1.98180629822108</v>
+        <v>1.96684468121868</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>-1.01175331091251</v>
+        <v>-1.45257228653135</v>
       </c>
       <c r="B80" t="n">
-        <v>-1.14936450316694</v>
+        <v>-0.877916219884523</v>
       </c>
       <c r="C80" t="n">
-        <v>1.61536187370335</v>
+        <v>1.12667608893806</v>
       </c>
       <c r="D80" t="n">
-        <v>1.28119399563043</v>
+        <v>1.71623298979338</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.09176672221983</v>
+        <v>-0.417569107940723</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.5121930170852</v>
+        <v>-0.976923092483552</v>
       </c>
       <c r="G80" t="n">
-        <v>1.97356919690659</v>
+        <v>1.91224847239249</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>-1.26356696194956</v>
+        <v>-1.15555388309889</v>
       </c>
       <c r="B81" t="n">
-        <v>-1.01351625225578</v>
+        <v>-0.853807613510593</v>
       </c>
       <c r="C81" t="n">
-        <v>1.16787807643695</v>
+        <v>0.88522270241074</v>
       </c>
       <c r="D81" t="n">
-        <v>1.63398828951029</v>
+        <v>1.06398754956645</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.857669576599682</v>
+        <v>-1.03389981132991</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.24423679914068</v>
+        <v>-1.26235768756957</v>
       </c>
       <c r="G81" t="n">
-        <v>1.88859715466073</v>
+        <v>2.04400542276881</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>-0.688691213344888</v>
+        <v>-0.654795487082644</v>
       </c>
       <c r="B82" t="n">
-        <v>-0.860191591999453</v>
+        <v>-0.915721645350545</v>
       </c>
       <c r="C82" t="n">
-        <v>1.44544849018557</v>
+        <v>1.13196709434007</v>
       </c>
       <c r="D82" t="n">
-        <v>0.65619886940595</v>
+        <v>0.583876754376337</v>
       </c>
       <c r="E82" t="n">
-        <v>-1.293622538048</v>
+        <v>-1.53929453139935</v>
       </c>
       <c r="F82" t="n">
-        <v>-1.64537392776142</v>
+        <v>-1.9578467532399</v>
       </c>
       <c r="G82" t="n">
-        <v>2.08473516648823</v>
+        <v>1.96101720799014</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>-1.47767648397204</v>
+        <v>-1.09722059622185</v>
       </c>
       <c r="B83" t="n">
-        <v>-1.26340331465337</v>
+        <v>-1.06865706990958</v>
       </c>
       <c r="C83" t="n">
-        <v>1.65855186139125</v>
+        <v>1.06698864438783</v>
       </c>
       <c r="D83" t="n">
-        <v>1.84617171175516</v>
+        <v>0.781872013842901</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.460520573958079</v>
+        <v>-0.959828047925105</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.816280942505895</v>
+        <v>-2.09357949569685</v>
       </c>
       <c r="G83" t="n">
-        <v>1.92899860081832</v>
+        <v>1.9623389198179</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>-1.13503776517735</v>
+        <v>-1.45097900073925</v>
       </c>
       <c r="B84" t="n">
-        <v>-0.694282772551912</v>
+        <v>-1.11338209680882</v>
       </c>
       <c r="C84" t="n">
-        <v>1.04956608222224</v>
+        <v>1.35668675806052</v>
       </c>
       <c r="D84" t="n">
-        <v>1.43320379464246</v>
+        <v>1.46186371557206</v>
       </c>
       <c r="E84" t="n">
-        <v>-1.09973443556275</v>
+        <v>-0.531053632351589</v>
       </c>
       <c r="F84" t="n">
-        <v>-2.07541589252839</v>
+        <v>-1.73088538656621</v>
       </c>
       <c r="G84" t="n">
-        <v>1.99620281606746</v>
+        <v>2.04158213536459</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>-1.24806336812175</v>
+        <v>-1.21339495518903</v>
       </c>
       <c r="B85" t="n">
-        <v>-1.05233701659983</v>
+        <v>-0.963587113957595</v>
       </c>
       <c r="C85" t="n">
-        <v>1.44433254802619</v>
+        <v>1.38507284160803</v>
       </c>
       <c r="D85" t="n">
-        <v>1.56550953430127</v>
+        <v>0.953885316555291</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.950475392424716</v>
+        <v>-0.573669802841761</v>
       </c>
       <c r="F85" t="n">
-        <v>-1.92596475234749</v>
+        <v>-1.65087713913132</v>
       </c>
       <c r="G85" t="n">
-        <v>2.03942112923533</v>
+        <v>2.27461985369689</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>-1.00669988789258</v>
+        <v>-0.986789859867946</v>
       </c>
       <c r="B86" t="n">
-        <v>-1.08732505394923</v>
+        <v>-1.10686595922828</v>
       </c>
       <c r="C86" t="n">
-        <v>1.71669453867917</v>
+        <v>1.27307765559527</v>
       </c>
       <c r="D86" t="n">
-        <v>1.07315708409921</v>
+        <v>1.11861146074838</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.923055507142825</v>
+        <v>-1.01777064587417</v>
       </c>
       <c r="F86" t="n">
-        <v>-1.43017927620894</v>
+        <v>-1.54848716726953</v>
       </c>
       <c r="G86" t="n">
-        <v>1.98005150583975</v>
+        <v>1.9905844350017</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>-0.736422924472306</v>
+        <v>-1.01249171581397</v>
       </c>
       <c r="B87" t="n">
-        <v>-0.943996416533665</v>
+        <v>-1.21212390073452</v>
       </c>
       <c r="C87" t="n">
-        <v>1.57762095263055</v>
+        <v>1.18679379388544</v>
       </c>
       <c r="D87" t="n">
-        <v>0.508497965209653</v>
+        <v>0.942388481337588</v>
       </c>
       <c r="E87" t="n">
-        <v>-1.10158514545507</v>
+        <v>-1.21941578565236</v>
       </c>
       <c r="F87" t="n">
-        <v>-1.69315030082282</v>
+        <v>-1.66401049212524</v>
       </c>
       <c r="G87" t="n">
-        <v>2.02597437091848</v>
+        <v>1.85073485750554</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>-1.10046057510081</v>
+        <v>-0.883489533252298</v>
       </c>
       <c r="B88" t="n">
-        <v>-1.09377602326246</v>
+        <v>-1.04766148748536</v>
       </c>
       <c r="C88" t="n">
-        <v>1.93566092342664</v>
+        <v>0.958788837651736</v>
       </c>
       <c r="D88" t="n">
-        <v>1.62515914745109</v>
+        <v>0.642338791991798</v>
       </c>
       <c r="E88" t="n">
-        <v>-1.11898140477486</v>
+        <v>-1.29175747279634</v>
       </c>
       <c r="F88" t="n">
-        <v>-1.99190796612791</v>
+        <v>-1.53390158133743</v>
       </c>
       <c r="G88" t="n">
-        <v>2.0596376738756</v>
+        <v>1.96780877295796</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>-1.38396855047825</v>
+        <v>-1.49655680956339</v>
       </c>
       <c r="B89" t="n">
-        <v>-1.16000963494658</v>
+        <v>-0.954554869105687</v>
       </c>
       <c r="C89" t="n">
-        <v>1.75551850411114</v>
+        <v>1.07619964564631</v>
       </c>
       <c r="D89" t="n">
-        <v>1.75882118025446</v>
+        <v>1.52203103939549</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.718073997090706</v>
+        <v>-0.288531557022048</v>
       </c>
       <c r="F89" t="n">
-        <v>-0.936955836470202</v>
+        <v>-0.731317265398644</v>
       </c>
       <c r="G89" t="n">
-        <v>1.97306052072668</v>
+        <v>2.0136084164385</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>-1.18743580670702</v>
+        <v>-1.3345284909902</v>
       </c>
       <c r="B90" t="n">
-        <v>-0.919678364831435</v>
+        <v>-1.01242076848066</v>
       </c>
       <c r="C90" t="n">
-        <v>1.42442444267864</v>
+        <v>0.9660184020276</v>
       </c>
       <c r="D90" t="n">
-        <v>1.24166671659113</v>
+        <v>1.66767266544252</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.868000508855926</v>
+        <v>-0.878391069267608</v>
       </c>
       <c r="F90" t="n">
-        <v>-1.80388796982343</v>
+        <v>-1.17569697000641</v>
       </c>
       <c r="G90" t="n">
-        <v>2.00305894757792</v>
+        <v>2.01496377989286</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>-0.585719612777055</v>
+        <v>-0.838225966274887</v>
       </c>
       <c r="B91" t="n">
-        <v>-0.953287641489943</v>
+        <v>-0.896841921750303</v>
       </c>
       <c r="C91" t="n">
-        <v>1.52807942837046</v>
+        <v>0.911762062257428</v>
       </c>
       <c r="D91" t="n">
-        <v>0.211247479834087</v>
+        <v>0.717718341999029</v>
       </c>
       <c r="E91" t="n">
-        <v>-1.4592776279199</v>
+        <v>-1.16303693847102</v>
       </c>
       <c r="F91" t="n">
-        <v>-2.6513905763245</v>
+        <v>-1.66713623720183</v>
       </c>
       <c r="G91" t="n">
-        <v>2.05561571019726</v>
+        <v>1.88373267003132</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>-0.721368498754798</v>
+        <v>-1.24335198674805</v>
       </c>
       <c r="B92" t="n">
-        <v>-1.00108305296035</v>
+        <v>-1.13748642978907</v>
       </c>
       <c r="C92" t="n">
-        <v>1.48222499502858</v>
+        <v>1.20307068367072</v>
       </c>
       <c r="D92" t="n">
-        <v>0.803870983781371</v>
+        <v>1.14050492227374</v>
       </c>
       <c r="E92" t="n">
-        <v>-1.17621488794538</v>
+        <v>-0.800230294989335</v>
       </c>
       <c r="F92" t="n">
-        <v>-1.74914610381424</v>
+        <v>-1.93863159794595</v>
       </c>
       <c r="G92" t="n">
-        <v>1.95644568650548</v>
+        <v>2.04899596249985</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>-1.92512720467953</v>
+        <v>-1.20020083234056</v>
       </c>
       <c r="B93" t="n">
-        <v>-1.1747705769917</v>
+        <v>-1.06125227655247</v>
       </c>
       <c r="C93" t="n">
-        <v>1.56015389220733</v>
+        <v>0.888439654813015</v>
       </c>
       <c r="D93" t="n">
-        <v>2.58411108716227</v>
+        <v>1.14112752090974</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.165550985541685</v>
+        <v>-0.864740546533091</v>
       </c>
       <c r="F93" t="n">
-        <v>-1.10413689475063</v>
+        <v>-1.12339576986457</v>
       </c>
       <c r="G93" t="n">
-        <v>1.8428370225516</v>
+        <v>1.93965313690495</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>-1.10701315590861</v>
+        <v>-0.983053894816266</v>
       </c>
       <c r="B94" t="n">
-        <v>-1.12969753838174</v>
+        <v>-0.799584141364483</v>
       </c>
       <c r="C94" t="n">
-        <v>1.7851471143793</v>
+        <v>0.772693627323</v>
       </c>
       <c r="D94" t="n">
-        <v>1.25617456863631</v>
+        <v>0.862984051373434</v>
       </c>
       <c r="E94" t="n">
-        <v>-1.0241116865318</v>
+        <v>-1.18199176307092</v>
       </c>
       <c r="F94" t="n">
-        <v>-1.91541539149106</v>
+        <v>-1.4571251007715</v>
       </c>
       <c r="G94" t="n">
-        <v>2.03496187446903</v>
+        <v>1.99803261144803</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>-1.05407245304026</v>
+        <v>-1.03581426547373</v>
       </c>
       <c r="B95" t="n">
-        <v>-0.983788844125947</v>
+        <v>-0.899079639740497</v>
       </c>
       <c r="C95" t="n">
-        <v>1.50398452186105</v>
+        <v>1.2396541721763</v>
       </c>
       <c r="D95" t="n">
-        <v>1.27359295245754</v>
+        <v>0.981137952146972</v>
       </c>
       <c r="E95" t="n">
-        <v>-1.18951039790261</v>
+        <v>-0.827754330578727</v>
       </c>
       <c r="F95" t="n">
-        <v>-2.39529217350252</v>
+        <v>-1.31142098319841</v>
       </c>
       <c r="G95" t="n">
-        <v>2.134190603709</v>
+        <v>2.1217757371196</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>-1.31870513233495</v>
+        <v>-0.99798221919727</v>
       </c>
       <c r="B96" t="n">
-        <v>-0.913452440431295</v>
+        <v>-0.946742106953392</v>
       </c>
       <c r="C96" t="n">
-        <v>1.48505935848898</v>
+        <v>1.03523424645754</v>
       </c>
       <c r="D96" t="n">
-        <v>1.78850284722558</v>
+        <v>0.818534297521916</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.694009146928944</v>
+        <v>-1.11910762945877</v>
       </c>
       <c r="F96" t="n">
-        <v>-1.15292815115159</v>
+        <v>-1.21477891495689</v>
       </c>
       <c r="G96" t="n">
-        <v>2.01783697018522</v>
+        <v>1.98244768586575</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>-1.06960094221235</v>
+        <v>-1.22336280814749</v>
       </c>
       <c r="B97" t="n">
-        <v>-0.998371851100859</v>
+        <v>-0.798060484273888</v>
       </c>
       <c r="C97" t="n">
-        <v>1.53729720607949</v>
+        <v>0.763207300336304</v>
       </c>
       <c r="D97" t="n">
-        <v>1.24519108422537</v>
+        <v>1.10348703720619</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.617385267530842</v>
+        <v>-0.89689088067165</v>
       </c>
       <c r="F97" t="n">
-        <v>-1.3084797018794</v>
+        <v>-1.08305427286589</v>
       </c>
       <c r="G97" t="n">
-        <v>1.91577445282601</v>
+        <v>1.94334869016852</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>-1.02029210951443</v>
+        <v>-0.889758390099975</v>
       </c>
       <c r="B98" t="n">
-        <v>-1.13867308245781</v>
+        <v>-0.799703503768099</v>
       </c>
       <c r="C98" t="n">
-        <v>1.67224077568186</v>
+        <v>0.902204697831642</v>
       </c>
       <c r="D98" t="n">
-        <v>1.02129583387108</v>
+        <v>1.03549610879669</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.906576133370578</v>
+        <v>-1.27568386400478</v>
       </c>
       <c r="F98" t="n">
-        <v>-1.27705417882992</v>
+        <v>-1.57553725415321</v>
       </c>
       <c r="G98" t="n">
-        <v>1.93480267553652</v>
+        <v>1.94611112560935</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>-0.855183600525387</v>
+        <v>-1.19894912622147</v>
       </c>
       <c r="B99" t="n">
-        <v>-0.850345222379402</v>
+        <v>-1.24920043246271</v>
       </c>
       <c r="C99" t="n">
-        <v>1.32489946019634</v>
+        <v>1.13360561902964</v>
       </c>
       <c r="D99" t="n">
-        <v>0.974366500940566</v>
+        <v>0.948952284225418</v>
       </c>
       <c r="E99" t="n">
-        <v>-1.40445487657521</v>
+        <v>-0.957963092945296</v>
       </c>
       <c r="F99" t="n">
-        <v>-2.45327283704348</v>
+        <v>-1.89705585458722</v>
       </c>
       <c r="G99" t="n">
-        <v>2.00207255821198</v>
+        <v>1.83354677219267</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>-1.19938306901467</v>
+        <v>-0.882233470205019</v>
       </c>
       <c r="B100" t="n">
-        <v>-1.07848086006201</v>
+        <v>-1.01416988925981</v>
       </c>
       <c r="C100" t="n">
-        <v>1.60045929438057</v>
+        <v>0.946357840520855</v>
       </c>
       <c r="D100" t="n">
-        <v>1.31813185745072</v>
+        <v>0.638903670814413</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.922391990455696</v>
+        <v>-1.02388898486097</v>
       </c>
       <c r="F100" t="n">
-        <v>-2.09572742948436</v>
+        <v>-1.56457260368145</v>
       </c>
       <c r="G100" t="n">
-        <v>2.03341076026785</v>
+        <v>1.96907041591872</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>-1.09895809146185</v>
+        <v>-0.988033015785448</v>
       </c>
       <c r="B101" t="n">
-        <v>-1.09682653330774</v>
+        <v>-0.931831263124262</v>
       </c>
       <c r="C101" t="n">
-        <v>1.43237495535732</v>
+        <v>1.09190094876942</v>
       </c>
       <c r="D101" t="n">
-        <v>1.27667645132888</v>
+        <v>0.966254332929782</v>
       </c>
       <c r="E101" t="n">
-        <v>-1.19608195042937</v>
+        <v>-1.04398713830552</v>
       </c>
       <c r="F101" t="n">
-        <v>-2.44761060000662</v>
+        <v>-1.34793381490181</v>
       </c>
       <c r="G101" t="n">
-        <v>1.84513612721057</v>
+        <v>2.01492163617049</v>
       </c>
     </row>
   </sheetData>
@@ -3149,826 +3152,826 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.348033030858755</v>
+        <v>0.284036640529202</v>
       </c>
       <c r="B2" t="n">
-        <v>0.228672368511259</v>
+        <v>0.210654089827359</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.309648078027193</v>
+        <v>63.9970905306168</v>
       </c>
       <c r="B3" t="n">
-        <v>0.17438300440128</v>
+        <v>0.458605902193667</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>11.6315684159219</v>
+        <v>0.705001550617193</v>
       </c>
       <c r="B4" t="n">
-        <v>0.314338604516173</v>
+        <v>0.102279470698977</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3.47746685187667</v>
+        <v>0.959628737527344</v>
       </c>
       <c r="B5" t="n">
-        <v>0.244437725068191</v>
+        <v>0.154374684554434</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>225.843704472957</v>
+        <v>0.321459842572495</v>
       </c>
       <c r="B6" t="n">
-        <v>0.395368096109676</v>
+        <v>0.58596320282432</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>13.792326863</v>
+        <v>0.415040769959883</v>
       </c>
       <c r="B7" t="n">
-        <v>0.312235925937947</v>
+        <v>0.210882349520211</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5.74773826599695</v>
+        <v>0.110069348158572</v>
       </c>
       <c r="B8" t="n">
-        <v>0.21678246743673</v>
+        <v>0.0635258534193822</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>436.056348938308</v>
+        <v>0.410957575571551</v>
       </c>
       <c r="B9" t="n">
-        <v>0.546617929728715</v>
+        <v>0.161764619851681</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>25.5066106561917</v>
+        <v>7.23309651329827</v>
       </c>
       <c r="B10" t="n">
-        <v>0.359309616537363</v>
+        <v>0.296459847366296</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3.11543442787885</v>
+        <v>0.603364452233952</v>
       </c>
       <c r="B11" t="n">
-        <v>0.188194591591013</v>
+        <v>0.353741320078529</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>83.3352104123256</v>
+        <v>1.18406231899116</v>
       </c>
       <c r="B12" t="n">
-        <v>0.438109142026594</v>
+        <v>0.225845752686028</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.333170444536004</v>
+        <v>0.495698628031909</v>
       </c>
       <c r="B13" t="n">
-        <v>0.245046884541383</v>
+        <v>0.404751743791121</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>8.54731154900949</v>
+        <v>5.56871219965854</v>
       </c>
       <c r="B14" t="n">
-        <v>0.284799109745105</v>
+        <v>0.242289181800362</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.485178774105737</v>
+        <v>51.8399993563246</v>
       </c>
       <c r="B15" t="n">
-        <v>0.112539187379774</v>
+        <v>0.41179102600631</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.661127531965221</v>
+        <v>0.136532167806223</v>
       </c>
       <c r="B16" t="n">
-        <v>0.339946219622524</v>
+        <v>0.210519719793872</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>484.21701223859</v>
+        <v>3.07077064313898</v>
       </c>
       <c r="B17" t="n">
-        <v>0.588343409938613</v>
+        <v>0.230360902192476</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.287524822416777</v>
+        <v>4.94683188531685</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0751391138130166</v>
+        <v>0.231299084690566</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>22.5372649526526</v>
+        <v>0.3973262554543</v>
       </c>
       <c r="B19" t="n">
-        <v>0.357282986784643</v>
+        <v>0.181882171496413</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.150974857804704</v>
+        <v>3.39948653785681</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0836978029089217</v>
+        <v>0.207000712735803</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.090793385510754</v>
+        <v>2.62628616733948</v>
       </c>
       <c r="B21" t="n">
-        <v>0.0478077976883688</v>
+        <v>0.214503816034764</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.301768318433675</v>
+        <v>0.868531856137997</v>
       </c>
       <c r="B22" t="n">
-        <v>0.136909425953288</v>
+        <v>0.313409597993659</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>15.6303525752158</v>
+        <v>0.715631280828877</v>
       </c>
       <c r="B23" t="n">
-        <v>0.303987679508922</v>
+        <v>0.107693713523292</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4.87792016158248</v>
+        <v>0.69670654513371</v>
       </c>
       <c r="B24" t="n">
-        <v>0.281194757094196</v>
+        <v>0.138398811286339</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>7.17538218333727</v>
+        <v>0.298923544974922</v>
       </c>
       <c r="B25" t="n">
-        <v>0.283111947278715</v>
+        <v>0.558771637240577</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1.51361880640433</v>
+        <v>7.91878017611312</v>
       </c>
       <c r="B26" t="n">
-        <v>0.153526978417312</v>
+        <v>0.329710260604397</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2.89552507426196</v>
+        <v>1.40162968160251</v>
       </c>
       <c r="B27" t="n">
-        <v>0.255669237021535</v>
+        <v>0.201033898272365</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.331568664909935</v>
+        <v>0.309582575103719</v>
       </c>
       <c r="B28" t="n">
-        <v>0.0920216738857631</v>
+        <v>0.243281009486727</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.29219674859914</v>
+        <v>7.29242622706073</v>
       </c>
       <c r="B29" t="n">
-        <v>0.107948447021161</v>
+        <v>0.299125870634208</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>61.4883338099678</v>
+        <v>4.59409085476577</v>
       </c>
       <c r="B30" t="n">
-        <v>0.488726308830234</v>
+        <v>0.253661882359038</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2.89927565575042</v>
+        <v>0.312958314234682</v>
       </c>
       <c r="B31" t="n">
-        <v>0.216834598084425</v>
+        <v>0.268640761767924</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>5.13751150182163</v>
+        <v>7.26795671576472</v>
       </c>
       <c r="B32" t="n">
-        <v>0.25340819894734</v>
+        <v>0.291284795099634</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.371800643811361</v>
+        <v>0.582148899934416</v>
       </c>
       <c r="B33" t="n">
-        <v>0.195480667291077</v>
+        <v>0.829463056475676</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>8.04403693759993</v>
+        <v>0.0401926288147414</v>
       </c>
       <c r="B34" t="n">
-        <v>0.290444507832722</v>
+        <v>0.0247873212644349</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>41.8251352973033</v>
+        <v>3.03941461811152</v>
       </c>
       <c r="B35" t="n">
-        <v>0.414864171028061</v>
+        <v>0.194313170477963</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1.21169345464722</v>
+        <v>14.0551912019997</v>
       </c>
       <c r="B36" t="n">
-        <v>0.145440295600454</v>
+        <v>0.321272608021729</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3.62146828594704</v>
+        <v>0.463740786289489</v>
       </c>
       <c r="B37" t="n">
-        <v>0.264979338527929</v>
+        <v>0.284684550812213</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>19.2826996527232</v>
+        <v>9.00844057004706</v>
       </c>
       <c r="B38" t="n">
-        <v>0.308967130239137</v>
+        <v>0.308540516327217</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.337593123082673</v>
+        <v>0.252038472689417</v>
       </c>
       <c r="B39" t="n">
-        <v>0.198694326695344</v>
+        <v>0.113341781265519</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.114180687589512</v>
+        <v>0.246779146517315</v>
       </c>
       <c r="B40" t="n">
-        <v>0.0619407514654057</v>
+        <v>0.0687989611132695</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>12.997337178632</v>
+        <v>24.3400528236858</v>
       </c>
       <c r="B41" t="n">
-        <v>0.285953751417049</v>
+        <v>0.364372438000342</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.420369806022802</v>
+        <v>0.242861086711879</v>
       </c>
       <c r="B42" t="n">
-        <v>0.323555254415562</v>
+        <v>0.0777151725934007</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.461152922733653</v>
+        <v>8.43441858985616</v>
       </c>
       <c r="B43" t="n">
-        <v>0.224403873960437</v>
+        <v>0.308796216732753</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>18.4897740781067</v>
+        <v>0.511835722178692</v>
       </c>
       <c r="B44" t="n">
-        <v>0.356238534565861</v>
+        <v>0.65648640474072</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2.45649907654535</v>
+        <v>0.462586930889128</v>
       </c>
       <c r="B45" t="n">
-        <v>0.173385663726417</v>
+        <v>0.354820941064565</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1.10716587787149</v>
+        <v>7.10985710503794</v>
       </c>
       <c r="B46" t="n">
-        <v>0.208697511106592</v>
+        <v>0.261364796336279</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.210654124034774</v>
+        <v>2.54860506226436</v>
       </c>
       <c r="B47" t="n">
-        <v>0.12528225756518</v>
+        <v>0.184276850048297</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.834871130818799</v>
+        <v>1.99050587863024</v>
       </c>
       <c r="B48" t="n">
-        <v>0.152760441223163</v>
+        <v>0.173300846464547</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3.72350429243443</v>
+        <v>0.469326430173662</v>
       </c>
       <c r="B49" t="n">
-        <v>0.206646602548635</v>
+        <v>0.250080443344689</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.597797775687686</v>
+        <v>36.3401666070463</v>
       </c>
       <c r="B50" t="n">
-        <v>0.23232082093048</v>
+        <v>0.395310142987847</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.406298898510939</v>
+        <v>1.24131837992121</v>
       </c>
       <c r="B51" t="n">
-        <v>0.204184903617124</v>
+        <v>0.150174981239924</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1.8490761245052</v>
+        <v>4.22875115476061</v>
       </c>
       <c r="B52" t="n">
-        <v>0.197161520236779</v>
+        <v>0.242294331843781</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.167340147796563</v>
+        <v>0.579390640519104</v>
       </c>
       <c r="B53" t="n">
-        <v>0.0669740332416295</v>
+        <v>0.903499766468836</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>89.4951482825222</v>
+        <v>1.43795789665398</v>
       </c>
       <c r="B54" t="n">
-        <v>0.447918501288321</v>
+        <v>0.173726679533644</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.821400402253625</v>
+        <v>0.818602375066747</v>
       </c>
       <c r="B55" t="n">
-        <v>0.324376850601839</v>
+        <v>0.197998604402146</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>4.44834027868484</v>
+        <v>7.09586057579099</v>
       </c>
       <c r="B56" t="n">
-        <v>0.413496081903353</v>
+        <v>0.262475476977013</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.426867057532468</v>
+        <v>0.777939605533711</v>
       </c>
       <c r="B57" t="n">
-        <v>0.22267284228333</v>
+        <v>0.205878787164918</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>7.9639218087574</v>
+        <v>4.45908262798374</v>
       </c>
       <c r="B58" t="n">
-        <v>0.264749232838475</v>
+        <v>0.261515444559609</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.138396612400189</v>
+        <v>27.0186880891081</v>
       </c>
       <c r="B59" t="n">
-        <v>0.0618475500675922</v>
+        <v>0.379364691773734</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>8.36460981498666</v>
+        <v>0.0410661348833396</v>
       </c>
       <c r="B60" t="n">
-        <v>0.301548421540223</v>
+        <v>0.0392656089555888</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>43.8931143562226</v>
+        <v>0.496032379178844</v>
       </c>
       <c r="B61" t="n">
-        <v>0.373896473850643</v>
+        <v>0.202021318589046</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.437825706633069</v>
+        <v>0.393387027833146</v>
       </c>
       <c r="B62" t="n">
-        <v>0.0787554057288714</v>
+        <v>0.0776744237682287</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>39.4610541639561</v>
+        <v>0.317123078727396</v>
       </c>
       <c r="B63" t="n">
-        <v>0.376451432922542</v>
+        <v>0.262802884179533</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.55529771160014</v>
+        <v>0.13311338000661</v>
       </c>
       <c r="B64" t="n">
-        <v>0.672673435887475</v>
+        <v>0.0521469339079586</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1.41123010134926</v>
+        <v>0.34824408093336</v>
       </c>
       <c r="B65" t="n">
-        <v>0.182382642652478</v>
+        <v>0.126748416805771</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>3.78262069925011</v>
+        <v>1.42937115940217</v>
       </c>
       <c r="B66" t="n">
-        <v>0.240835957327696</v>
+        <v>0.157986950705193</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>79.2472894831445</v>
+        <v>4.74552111626104</v>
       </c>
       <c r="B67" t="n">
-        <v>0.388896800573433</v>
+        <v>0.283210499876359</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>51.626493330409</v>
+        <v>7.27067578734299</v>
       </c>
       <c r="B68" t="n">
-        <v>0.411100834332658</v>
+        <v>0.279598394635332</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.397973111482322</v>
+        <v>0.440981364066388</v>
       </c>
       <c r="B69" t="n">
-        <v>0.266341629922683</v>
+        <v>0.271172545067492</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.140335649879688</v>
+        <v>0.303850772285554</v>
       </c>
       <c r="B70" t="n">
-        <v>0.125804131637615</v>
+        <v>0.108505116827953</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>32.6545410589516</v>
+        <v>0.868096352240618</v>
       </c>
       <c r="B71" t="n">
-        <v>0.263975104423</v>
+        <v>0.229120431612672</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.945852919099461</v>
+        <v>21.9313267589161</v>
       </c>
       <c r="B72" t="n">
-        <v>0.336500413403551</v>
+        <v>0.396347750565797</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>18.7745950955964</v>
+        <v>479.578416507095</v>
       </c>
       <c r="B73" t="n">
-        <v>0.407636096581589</v>
+        <v>0.576740829914949</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>9.45124569491883</v>
+        <v>0.811819104037944</v>
       </c>
       <c r="B74" t="n">
-        <v>0.303350458985532</v>
+        <v>0.133938929406014</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.337559043543929</v>
+        <v>2.17595920401168</v>
       </c>
       <c r="B75" t="n">
-        <v>0.310721052069816</v>
+        <v>0.215020762478146</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>10.7051034093474</v>
+        <v>7.50321211799288</v>
       </c>
       <c r="B76" t="n">
-        <v>0.30578348661803</v>
+        <v>0.287845436068226</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>10.3281915806148</v>
+        <v>1.28868548976752</v>
       </c>
       <c r="B77" t="n">
-        <v>0.232156300545808</v>
+        <v>0.147318471403667</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.228783118237815</v>
+        <v>9.20122163353512</v>
       </c>
       <c r="B78" t="n">
-        <v>0.147948720040171</v>
+        <v>0.272170773827403</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>14.7205970182925</v>
+        <v>3.89276069340233</v>
       </c>
       <c r="B79" t="n">
-        <v>0.308880679694671</v>
+        <v>0.243821781410863</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>4.59045328762738</v>
+        <v>0.368300518015864</v>
       </c>
       <c r="B80" t="n">
-        <v>0.24285776991967</v>
+        <v>0.305973854079422</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>4.253843327249</v>
+        <v>0.111280676010262</v>
       </c>
       <c r="B81" t="n">
-        <v>0.234158874026347</v>
+        <v>0.0621059384570741</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>27.0732940478661</v>
+        <v>260.719095051034</v>
       </c>
       <c r="B82" t="n">
-        <v>0.350735640952134</v>
+        <v>0.525197947966361</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0.381332609361731</v>
+        <v>0.459153238459612</v>
       </c>
       <c r="B83" t="n">
-        <v>0.522503861178603</v>
+        <v>0.190477129145433</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1.95958322204062</v>
+        <v>0.333642995945888</v>
       </c>
       <c r="B84" t="n">
-        <v>0.227708707101189</v>
+        <v>0.326380332173305</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>0.396884163071559</v>
+        <v>0.426563756677376</v>
       </c>
       <c r="B85" t="n">
-        <v>0.205635319022856</v>
+        <v>0.35154821212228</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1.95887931285048</v>
+        <v>6.21702750971738</v>
       </c>
       <c r="B86" t="n">
-        <v>0.184406659015851</v>
+        <v>0.277166393668934</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>22.4479578200419</v>
+        <v>10.1442941615025</v>
       </c>
       <c r="B87" t="n">
-        <v>0.366053378270727</v>
+        <v>0.361051221486529</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>3.48962797251964</v>
+        <v>6.10329889212448</v>
       </c>
       <c r="B88" t="n">
-        <v>0.191043130976559</v>
+        <v>0.284070610190658</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>0.397145652084166</v>
+        <v>0.594748846693182</v>
       </c>
       <c r="B89" t="n">
-        <v>0.348278976851973</v>
+        <v>0.689881425520041</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>0.340286704070599</v>
+        <v>0.166452070903853</v>
       </c>
       <c r="B90" t="n">
-        <v>0.204931983970289</v>
+        <v>0.0771013070600558</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>244.192680016723</v>
+        <v>31.2094874171184</v>
       </c>
       <c r="B91" t="n">
-        <v>0.512915462749088</v>
+        <v>0.355343765315302</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>53.5293417415985</v>
+        <v>0.298462392256565</v>
       </c>
       <c r="B92" t="n">
-        <v>0.418010042770335</v>
+        <v>0.241109192957725</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>0.356916870662793</v>
+        <v>0.22145389198678</v>
       </c>
       <c r="B93" t="n">
-        <v>1.00670182369104</v>
+        <v>0.120189397133231</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>0.58307743155281</v>
+        <v>3.25727787340408</v>
       </c>
       <c r="B94" t="n">
-        <v>0.184823756986349</v>
+        <v>0.215569428066203</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>4.78649850035345</v>
+        <v>0.453293715009831</v>
       </c>
       <c r="B95" t="n">
-        <v>0.346832654208638</v>
+        <v>0.104855935113385</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>0.291642596376975</v>
+        <v>0.0421827461487157</v>
       </c>
       <c r="B96" t="n">
-        <v>0.115686943786812</v>
+        <v>0.0326682057347795</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>0.459604584726799</v>
+        <v>0.347962855760356</v>
       </c>
       <c r="B97" t="n">
-        <v>0.0916872638703734</v>
+        <v>0.175472516879685</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>0.367854303275873</v>
+        <v>14.184143902585</v>
       </c>
       <c r="B98" t="n">
-        <v>0.0801279007551138</v>
+        <v>0.299446708984086</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>46.4808649963896</v>
+        <v>0.369324431019918</v>
       </c>
       <c r="B99" t="n">
-        <v>0.450898968468458</v>
+        <v>0.183109909426429</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>0.628798769174349</v>
+        <v>7.87793594604579</v>
       </c>
       <c r="B100" t="n">
-        <v>0.208639225347582</v>
+        <v>0.283124332094867</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>12.9342223456966</v>
+        <v>0.97508185508988</v>
       </c>
       <c r="B101" t="n">
-        <v>0.447802120093813</v>
+        <v>0.136786456335832</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>24.102075297716</v>
+        <v>12.2622975268437</v>
       </c>
       <c r="B104" t="n">
-        <v>0.274779085953004</v>
+        <v>0.260742511517836</v>
       </c>
     </row>
   </sheetData>
@@ -3984,18 +3987,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46016.9144535616</v>
+        <v>46026.214220875</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
